--- a/results/Int All Data -0.2/Rando_7_permute.xlsx
+++ b/results/Int All Data -0.2/Rando_7_permute.xlsx
@@ -440,687 +440,687 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9268933491818121</v>
+        <v>0.9264681911589303</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9315397043396501</v>
+        <v>0.9251863530638682</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9330588590327091</v>
+        <v>0.9251863530638682</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9362494944704822</v>
+        <v>0.9241621553931018</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9382560104123684</v>
+        <v>0.9168544054459643</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9360197736459508</v>
+        <v>0.9187911223884396</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9363611728695396</v>
+        <v>0.9093512183004764</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9348559779763628</v>
+        <v>0.9099362981484789</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9287945507510578</v>
+        <v>0.9106051367957743</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9287945507510578</v>
+        <v>0.9125139341384854</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9287945507510578</v>
+        <v>0.9198496036853872</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9287945507510578</v>
+        <v>0.9201630833092116</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9291219901747644</v>
+        <v>0.9210895623808029</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9271433938326425</v>
+        <v>0.9272969516313463</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9237852407962834</v>
+        <v>0.9261750353614049</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9273591548572918</v>
+        <v>0.9255341163138737</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9302781900708871</v>
+        <v>0.9291778293742929</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9290242715755892</v>
+        <v>0.9275825116554064</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9243284412446393</v>
+        <v>0.9197937644858585</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9282716741290009</v>
+        <v>0.9207481631572141</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9267321956096429</v>
+        <v>0.9207481631572141</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9273870744570561</v>
+        <v>0.9226290409001607</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9260633569623475</v>
+        <v>0.9281675915034089</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9247256796677568</v>
+        <v>0.9281675915034089</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9272195568584702</v>
+        <v>0.9265583139846401</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9280076696782882</v>
+        <v>0.8941481750641022</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9250188354652822</v>
+        <v>0.8941481750641022</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9240783965938089</v>
+        <v>0.8964402510300484</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9231176338960364</v>
+        <v>0.8938131398669302</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9231176338960364</v>
+        <v>0.8867769901439707</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9240859923672742</v>
+        <v>0.8867769901439707</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9267753067563379</v>
+        <v>0.8893546261339771</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9303695446436453</v>
+        <v>0.8904968662302176</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.930445707669473</v>
+        <v>0.9004177675405911</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9281536317035267</v>
+        <v>0.9003898479408269</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9281815513032909</v>
+        <v>0.9010447267882401</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9159482502006722</v>
+        <v>0.9057265973193078</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.917926846542794</v>
+        <v>0.9057265973193078</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9226011213003964</v>
+        <v>0.9028634013052412</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.917926846542794</v>
+        <v>0.9031768809290657</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9191528454383275</v>
+        <v>0.9061238357424253</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9227686388989824</v>
+        <v>0.9077749926608405</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9260569929359306</v>
+        <v>0.9081024320845472</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9257155937123418</v>
+        <v>0.9071201138134273</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9247535992675211</v>
+        <v>0.8903648640048613</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9290801107751179</v>
+        <v>0.8900234647812725</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.9300484692463555</v>
+        <v>0.8900234647812725</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.9291080303748822</v>
+        <v>0.8897518645570945</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.9228803172980397</v>
+        <v>0.8913890616756277</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.9226924758731547</v>
+        <v>0.8986764877964661</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.92336131452045</v>
+        <v>0.8976802097254641</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.9220236372258593</v>
+        <v>0.9016792818093543</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.9235910353449815</v>
+        <v>0.9069322723885422</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.9171958046695531</v>
+        <v>0.9095797073779596</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.9055970585880484</v>
+        <v>0.9095517877781952</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.9062100580358151</v>
+        <v>0.9063471925405399</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.9036603416455731</v>
+        <v>0.8947611745118689</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8978577865916122</v>
+        <v>0.8887911018593222</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8981014672160259</v>
+        <v>0.8894320209068532</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.9041832182676299</v>
+        <v>0.8852311475981959</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8883417194778214</v>
+        <v>0.8972144040499843</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8723327030894269</v>
+        <v>0.8945530092606848</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8723327030894269</v>
+        <v>0.8948322052583282</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8562056442755583</v>
+        <v>0.8990889177665142</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8612073584568672</v>
+        <v>0.8990609981667498</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8462352677920728</v>
+        <v>0.867848938541981</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8487710243824328</v>
+        <v>0.8659959803987987</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8566295705513916</v>
+        <v>0.8663234198225053</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8566295705513916</v>
+        <v>0.8473586211002375</v>
       </c>
     </row>
     <row r="71">
@@ -1130,67 +1130,67 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8504640607004945</v>
+        <v>0.8551752878695498</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8507356609246726</v>
+        <v>0.8525418126800146</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8509374621494397</v>
+        <v>0.8492394988431842</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8534935425660987</v>
+        <v>0.8598507943742006</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8427020013836626</v>
+        <v>0.864970550980984</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8443252387023135</v>
+        <v>0.8652840306048084</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8456210365972577</v>
+        <v>0.8583380037075586</v>
       </c>
     </row>
     <row r="78">
@@ -1200,787 +1200,787 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.845112119775083</v>
+        <v>0.8537259321759016</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.847104675917087</v>
+        <v>0.8331315321085662</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8510339490015664</v>
+        <v>0.8383984824876363</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.832774736046872</v>
+        <v>0.8095419338018078</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.832774736046872</v>
+        <v>0.8089428941539232</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8334994138936962</v>
+        <v>0.8319613724125614</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.8296754551818573</v>
+        <v>0.8187660768651217</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8395608411190012</v>
+        <v>0.8134851666861693</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.8344055691389882</v>
+        <v>0.8074173754344475</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.8407741119617009</v>
+        <v>0.8054527388922078</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.8330627595650291</v>
+        <v>0.8054527388922078</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.8355845563555069</v>
+        <v>0.8051252994685012</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.8395544770925842</v>
+        <v>0.7930240005912386</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.8373042805262845</v>
+        <v>0.7988062318189004</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.8330132843919174</v>
+        <v>0.7974964741240739</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.8333267640157418</v>
+        <v>0.7522539944530324</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.8024355744970879</v>
+        <v>0.6961501746001442</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.8085364176279426</v>
+        <v>0.7148142217514212</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.805673221613876</v>
+        <v>0.7190848940594893</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7708351039697154</v>
+        <v>0.7253202029097972</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7724647053147833</v>
+        <v>0.7093035907479374</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7721512256909587</v>
+        <v>0.7164932982696006</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7781225300905539</v>
+        <v>0.701117605155272</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7778457975870076</v>
+        <v>0.702113883226274</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7796847959303077</v>
+        <v>0.7404522153997122</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7593860151545945</v>
+        <v>0.7332066686785201</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.7427843231447323</v>
+        <v>0.7377768608105306</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.7427843231447323</v>
+        <v>0.7450084477318405</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.7406876843771364</v>
+        <v>0.7443675286843094</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6944450261027728</v>
+        <v>0.7482968017687888</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6870878009825235</v>
+        <v>0.7486521607922596</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6724862608881307</v>
+        <v>0.75293679290021</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6631580351992248</v>
+        <v>0.7545600302188609</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6650807923418181</v>
+        <v>0.7545600302188609</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6912759462383472</v>
+        <v>0.7506167973344994</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6875700299519824</v>
+        <v>0.7947589163089468</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6026817186155984</v>
+        <v>0.7913664796464065</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6076834327969075</v>
+        <v>0.7910390402226999</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.6095643105398542</v>
+        <v>0.7687173202111215</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5970390853867583</v>
+        <v>0.7741238685890133</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.6052174752059584</v>
+        <v>0.7832730803735479</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.6061579140774317</v>
+        <v>0.7596097825350586</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.6115632307082751</v>
+        <v>0.7675317636770114</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5921529501368266</v>
+        <v>0.7675317636770114</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5650426081833169</v>
+        <v>0.7079971177119067</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5580978130331156</v>
+        <v>0.7146918682112775</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5580978130331156</v>
+        <v>0.7143504689876887</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5417385699006185</v>
+        <v>0.7140369893638643</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5476743589269841</v>
+        <v>0.6230314116026466</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5527039927080575</v>
+        <v>0.6233448912264711</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5341477234235177</v>
+        <v>0.6203369649342144</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5341477234235177</v>
+        <v>0.6203369649342144</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5303999277375064</v>
+        <v>0.6150712463021927</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5157971558960652</v>
+        <v>0.5653599883394612</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5158529950955938</v>
+        <v>0.5544580005050163</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5221695992510978</v>
+        <v>0.5578592646880703</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5071492651602401</v>
+        <v>0.5525440708829368</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4959896369014992</v>
+        <v>0.5552333852720005</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5058965784119906</v>
+        <v>0.5154011492199961</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4975658625411352</v>
+        <v>0.5079474372476201</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4940960311057188</v>
+        <v>0.5084347984964475</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5022401372987376</v>
+        <v>0.4969058514143536</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4967091824689548</v>
+        <v>0.4959654125428802</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4853401572119816</v>
+        <v>0.4969756504137643</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5008135689254855</v>
+        <v>0.4989961261555327</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5014405281731343</v>
+        <v>0.4989263271561219</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5001307704783079</v>
+        <v>0.4989402869560041</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4982778123351255</v>
+        <v>0.5012184031220682</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4962712963932394</v>
+        <v>0.5016296013450678</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4965847760170638</v>
+        <v>0.5010305616971832</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5015534383192402</v>
+        <v>0.5010305616971832</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5015534383192402</v>
+        <v>0.5008008408726518</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5015534383192402</v>
+        <v>0.4989339229295872</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5015534383192402</v>
+        <v>0.5004873612488273</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5015534383192402</v>
+        <v>0.4998045628016497</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.501184119495887</v>
+        <v>0.501455719720065</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.501184119495887</v>
+        <v>0.5014417599201828</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5005711200481203</v>
+        <v>0.5015255187194758</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5008985594718269</v>
+        <v>0.5011561998961226</v>
       </c>
     </row>
   </sheetData>
